--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T14:16:19+00:00</t>
+    <t>2025-02-13T08:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:25:30+00:00</t>
+    <t>2025-02-13T08:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="399">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:54:32+00:00</t>
+    <t>2025-02-14T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,10 +676,10 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>A code to identify a specific procedure .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/procedures-uv-ips</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -3717,11 +3717,9 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y19" t="s" s="2">
         <v>212</v>
       </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
         <v>213</v>
       </c>
@@ -5533,7 +5531,7 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="Y35" t="s" s="2">
         <v>326</v>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T08:32:04+00:00</t>
+    <t>2025-02-14T09:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-Procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
